--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123464683</v>
+        <v>123465014</v>
       </c>
       <c r="B2" t="n">
         <v>57851</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376582</v>
+        <v>376598</v>
       </c>
       <c r="R2" t="n">
-        <v>6391932</v>
+        <v>6391950</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123464802</v>
+        <v>123465129</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57984</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376470</v>
+        <v>376477</v>
       </c>
       <c r="R3" t="n">
-        <v>6391704</v>
+        <v>6391604</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123465409</v>
+        <v>123464683</v>
       </c>
       <c r="B4" t="n">
-        <v>57984</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,20 +909,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376319</v>
+        <v>376582</v>
       </c>
       <c r="R4" t="n">
-        <v>6391481</v>
+        <v>6391932</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123465291</v>
+        <v>123465281</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>56824</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100065</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376510</v>
+        <v>376361</v>
       </c>
       <c r="R5" t="n">
-        <v>6391640</v>
+        <v>6391616</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123465281</v>
+        <v>123464851</v>
       </c>
       <c r="B6" t="n">
-        <v>56824</v>
+        <v>57851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100065</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376361</v>
+        <v>375765</v>
       </c>
       <c r="R6" t="n">
-        <v>6391616</v>
+        <v>6391436</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1233,7 +1233,7 @@
         <v>123465181</v>
       </c>
       <c r="B7" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>123464849</v>
       </c>
       <c r="B8" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123465014</v>
+        <v>123465291</v>
       </c>
       <c r="B10" t="n">
         <v>57851</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376598</v>
+        <v>376510</v>
       </c>
       <c r="R10" t="n">
-        <v>6391950</v>
+        <v>6391640</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123464851</v>
+        <v>123464802</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,20 +1686,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375765</v>
+        <v>376470</v>
       </c>
       <c r="R11" t="n">
-        <v>6391436</v>
+        <v>6391704</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123465129</v>
+        <v>123465409</v>
       </c>
       <c r="B12" t="n">
         <v>57984</v>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376477</v>
+        <v>376319</v>
       </c>
       <c r="R12" t="n">
-        <v>6391604</v>
+        <v>6391481</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123465014</v>
+        <v>123464683</v>
       </c>
       <c r="B2" t="n">
         <v>57851</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376598</v>
+        <v>376582</v>
       </c>
       <c r="R2" t="n">
-        <v>6391950</v>
+        <v>6391932</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123465129</v>
+        <v>123465281</v>
       </c>
       <c r="B3" t="n">
-        <v>57984</v>
+        <v>56824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102995</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376477</v>
+        <v>376361</v>
       </c>
       <c r="R3" t="n">
-        <v>6391604</v>
+        <v>6391616</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123464683</v>
+        <v>123465409</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57984</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,20 +909,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376582</v>
+        <v>376319</v>
       </c>
       <c r="R4" t="n">
-        <v>6391932</v>
+        <v>6391481</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123465281</v>
+        <v>123464851</v>
       </c>
       <c r="B5" t="n">
-        <v>56824</v>
+        <v>57851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100065</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376361</v>
+        <v>375765</v>
       </c>
       <c r="R5" t="n">
-        <v>6391616</v>
+        <v>6391436</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123464851</v>
+        <v>123465129</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57984</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,20 +1131,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>102995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375765</v>
+        <v>376477</v>
       </c>
       <c r="R6" t="n">
-        <v>6391436</v>
+        <v>6391604</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123465181</v>
+        <v>123464678</v>
       </c>
       <c r="B7" t="n">
-        <v>97330</v>
+        <v>57851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,26 +1246,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375707</v>
+        <v>376617</v>
       </c>
       <c r="R7" t="n">
-        <v>6391364</v>
+        <v>6391973</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1344,7 +1344,7 @@
         <v>123464849</v>
       </c>
       <c r="B8" t="n">
-        <v>97330</v>
+        <v>97333</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123464678</v>
+        <v>123465291</v>
       </c>
       <c r="B9" t="n">
         <v>57851</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376617</v>
+        <v>376510</v>
       </c>
       <c r="R9" t="n">
-        <v>6391973</v>
+        <v>6391640</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123465291</v>
+        <v>123465014</v>
       </c>
       <c r="B10" t="n">
         <v>57851</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376510</v>
+        <v>376598</v>
       </c>
       <c r="R10" t="n">
-        <v>6391640</v>
+        <v>6391950</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123464802</v>
+        <v>123465181</v>
       </c>
       <c r="B11" t="n">
-        <v>57497</v>
+        <v>97333</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376470</v>
+        <v>375707</v>
       </c>
       <c r="R11" t="n">
-        <v>6391704</v>
+        <v>6391364</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123465409</v>
+        <v>123464802</v>
       </c>
       <c r="B12" t="n">
-        <v>57984</v>
+        <v>57497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,16 +1801,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102995</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376319</v>
+        <v>376470</v>
       </c>
       <c r="R12" t="n">
-        <v>6391481</v>
+        <v>6391704</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123464683</v>
+        <v>123464802</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376582</v>
+        <v>376470</v>
       </c>
       <c r="R2" t="n">
-        <v>6391932</v>
+        <v>6391704</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123465281</v>
+        <v>123464849</v>
       </c>
       <c r="B3" t="n">
-        <v>56824</v>
+        <v>97350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100065</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376361</v>
+        <v>375785</v>
       </c>
       <c r="R3" t="n">
-        <v>6391616</v>
+        <v>6391437</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123465409</v>
+        <v>123465014</v>
       </c>
       <c r="B4" t="n">
-        <v>57984</v>
+        <v>57857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,20 +909,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376319</v>
+        <v>376598</v>
       </c>
       <c r="R4" t="n">
-        <v>6391481</v>
+        <v>6391950</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123464851</v>
+        <v>123465181</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>97350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,26 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375765</v>
+        <v>375707</v>
       </c>
       <c r="R5" t="n">
-        <v>6391436</v>
+        <v>6391364</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>123465129</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
+        <v>57990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123464678</v>
+        <v>123465281</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>56830</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100065</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376617</v>
+        <v>376361</v>
       </c>
       <c r="R7" t="n">
-        <v>6391973</v>
+        <v>6391616</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123464849</v>
+        <v>123464683</v>
       </c>
       <c r="B8" t="n">
-        <v>97333</v>
+        <v>57857</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>375785</v>
+        <v>376582</v>
       </c>
       <c r="R8" t="n">
-        <v>6391437</v>
+        <v>6391932</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123465291</v>
+        <v>123464851</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376510</v>
+        <v>375765</v>
       </c>
       <c r="R9" t="n">
-        <v>6391640</v>
+        <v>6391436</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123465014</v>
+        <v>123465291</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376598</v>
+        <v>376510</v>
       </c>
       <c r="R10" t="n">
-        <v>6391950</v>
+        <v>6391640</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123465181</v>
+        <v>123465409</v>
       </c>
       <c r="B11" t="n">
-        <v>97333</v>
+        <v>57990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>102995</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375707</v>
+        <v>376319</v>
       </c>
       <c r="R11" t="n">
-        <v>6391364</v>
+        <v>6391481</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123464802</v>
+        <v>123464678</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>57857</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,20 +1797,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376470</v>
+        <v>376617</v>
       </c>
       <c r="R12" t="n">
-        <v>6391704</v>
+        <v>6391973</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123464802</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123464849</v>
+        <v>123465014</v>
       </c>
       <c r="B3" t="n">
-        <v>97350</v>
+        <v>57860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375785</v>
+        <v>376598</v>
       </c>
       <c r="R3" t="n">
-        <v>6391437</v>
+        <v>6391950</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123465014</v>
+        <v>123464678</v>
       </c>
       <c r="B4" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376598</v>
+        <v>376617</v>
       </c>
       <c r="R4" t="n">
-        <v>6391950</v>
+        <v>6391973</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123465181</v>
+        <v>123464851</v>
       </c>
       <c r="B5" t="n">
-        <v>97350</v>
+        <v>57860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,26 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375707</v>
+        <v>375765</v>
       </c>
       <c r="R5" t="n">
-        <v>6391364</v>
+        <v>6391436</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>123465129</v>
       </c>
       <c r="B6" t="n">
-        <v>57990</v>
+        <v>57993</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>123465281</v>
       </c>
       <c r="B7" t="n">
-        <v>56830</v>
+        <v>56833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123464683</v>
+        <v>123464849</v>
       </c>
       <c r="B8" t="n">
-        <v>57857</v>
+        <v>97367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376582</v>
+        <v>375785</v>
       </c>
       <c r="R8" t="n">
-        <v>6391932</v>
+        <v>6391437</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123464851</v>
+        <v>123465181</v>
       </c>
       <c r="B9" t="n">
-        <v>57857</v>
+        <v>97367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,26 +1468,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>375765</v>
+        <v>375707</v>
       </c>
       <c r="R9" t="n">
-        <v>6391436</v>
+        <v>6391364</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1566,7 +1566,7 @@
         <v>123465291</v>
       </c>
       <c r="B10" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>123465409</v>
       </c>
       <c r="B11" t="n">
-        <v>57990</v>
+        <v>57993</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123464678</v>
+        <v>123464683</v>
       </c>
       <c r="B12" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376617</v>
+        <v>376582</v>
       </c>
       <c r="R12" t="n">
-        <v>6391973</v>
+        <v>6391932</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123464802</v>
+        <v>123464683</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376470</v>
+        <v>376582</v>
       </c>
       <c r="R2" t="n">
-        <v>6391704</v>
+        <v>6391932</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123465014</v>
+        <v>123465291</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376598</v>
+        <v>376510</v>
       </c>
       <c r="R3" t="n">
-        <v>6391950</v>
+        <v>6391640</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123464678</v>
+        <v>123464849</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>97369</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,26 +913,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376617</v>
+        <v>375785</v>
       </c>
       <c r="R4" t="n">
-        <v>6391973</v>
+        <v>6391437</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123464851</v>
+        <v>123465409</v>
       </c>
       <c r="B5" t="n">
-        <v>57860</v>
+        <v>57994</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>102995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375765</v>
+        <v>376319</v>
       </c>
       <c r="R5" t="n">
-        <v>6391436</v>
+        <v>6391481</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123465129</v>
+        <v>123464802</v>
       </c>
       <c r="B6" t="n">
-        <v>57993</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102995</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376477</v>
+        <v>376470</v>
       </c>
       <c r="R6" t="n">
-        <v>6391604</v>
+        <v>6391704</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123465281</v>
+        <v>123464851</v>
       </c>
       <c r="B7" t="n">
-        <v>56833</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100065</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376361</v>
+        <v>375765</v>
       </c>
       <c r="R7" t="n">
-        <v>6391616</v>
+        <v>6391436</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123464849</v>
+        <v>123465281</v>
       </c>
       <c r="B8" t="n">
-        <v>97367</v>
+        <v>56834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100065</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>375785</v>
+        <v>376361</v>
       </c>
       <c r="R8" t="n">
-        <v>6391437</v>
+        <v>6391616</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123465181</v>
+        <v>123465014</v>
       </c>
       <c r="B9" t="n">
-        <v>97367</v>
+        <v>57861</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>375707</v>
+        <v>376598</v>
       </c>
       <c r="R9" t="n">
-        <v>6391364</v>
+        <v>6391950</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123465291</v>
+        <v>123465129</v>
       </c>
       <c r="B10" t="n">
-        <v>57860</v>
+        <v>57994</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,20 +1575,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>102995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376510</v>
+        <v>376477</v>
       </c>
       <c r="R10" t="n">
-        <v>6391640</v>
+        <v>6391604</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123465409</v>
+        <v>123465181</v>
       </c>
       <c r="B11" t="n">
-        <v>57993</v>
+        <v>97369</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102995</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376319</v>
+        <v>375707</v>
       </c>
       <c r="R11" t="n">
-        <v>6391481</v>
+        <v>6391364</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123464683</v>
+        <v>123464678</v>
       </c>
       <c r="B12" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376582</v>
+        <v>376617</v>
       </c>
       <c r="R12" t="n">
-        <v>6391932</v>
+        <v>6391973</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123465291</v>
+        <v>123464849</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>97369</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376510</v>
+        <v>375785</v>
       </c>
       <c r="R3" t="n">
-        <v>6391640</v>
+        <v>6391437</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123464849</v>
+        <v>123465291</v>
       </c>
       <c r="B4" t="n">
-        <v>97369</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,26 +913,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375785</v>
+        <v>376510</v>
       </c>
       <c r="R4" t="n">
-        <v>6391437</v>
+        <v>6391640</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123464683</v>
+        <v>123464849</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376582</v>
+        <v>375785</v>
       </c>
       <c r="R2" t="n">
-        <v>6391932</v>
+        <v>6391437</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123464849</v>
+        <v>123465291</v>
       </c>
       <c r="B3" t="n">
-        <v>97369</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375785</v>
+        <v>376510</v>
       </c>
       <c r="R3" t="n">
-        <v>6391437</v>
+        <v>6391640</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123465291</v>
+        <v>123465014</v>
       </c>
       <c r="B4" t="n">
         <v>57861</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376510</v>
+        <v>376598</v>
       </c>
       <c r="R4" t="n">
-        <v>6391640</v>
+        <v>6391950</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123465409</v>
+        <v>123465129</v>
       </c>
       <c r="B5" t="n">
         <v>57994</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376319</v>
+        <v>376477</v>
       </c>
       <c r="R5" t="n">
-        <v>6391481</v>
+        <v>6391604</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123464802</v>
+        <v>123465181</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>96957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376470</v>
+        <v>375707</v>
       </c>
       <c r="R6" t="n">
-        <v>6391704</v>
+        <v>6391364</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123464851</v>
+        <v>123465409</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>57994</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>102995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375765</v>
+        <v>376319</v>
       </c>
       <c r="R7" t="n">
-        <v>6391436</v>
+        <v>6391481</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123465281</v>
+        <v>123464678</v>
       </c>
       <c r="B8" t="n">
-        <v>56834</v>
+        <v>57861</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,16 +1357,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100065</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376361</v>
+        <v>376617</v>
       </c>
       <c r="R8" t="n">
-        <v>6391616</v>
+        <v>6391973</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123465014</v>
+        <v>123464802</v>
       </c>
       <c r="B9" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,20 +1464,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376598</v>
+        <v>376470</v>
       </c>
       <c r="R9" t="n">
-        <v>6391950</v>
+        <v>6391704</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123465129</v>
+        <v>123464683</v>
       </c>
       <c r="B10" t="n">
-        <v>57994</v>
+        <v>57861</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,20 +1575,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102995</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376477</v>
+        <v>376582</v>
       </c>
       <c r="R10" t="n">
-        <v>6391604</v>
+        <v>6391932</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123465181</v>
+        <v>123464851</v>
       </c>
       <c r="B11" t="n">
-        <v>97369</v>
+        <v>57861</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,26 +1690,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375707</v>
+        <v>375765</v>
       </c>
       <c r="R11" t="n">
-        <v>6391364</v>
+        <v>6391436</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123464678</v>
+        <v>123465281</v>
       </c>
       <c r="B12" t="n">
-        <v>57861</v>
+        <v>56834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,16 +1801,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>100065</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376617</v>
+        <v>376361</v>
       </c>
       <c r="R12" t="n">
-        <v>6391973</v>
+        <v>6391616</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123464849</v>
+        <v>123464802</v>
       </c>
       <c r="B2" t="n">
-        <v>96957</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375785</v>
+        <v>376470</v>
       </c>
       <c r="R2" t="n">
-        <v>6391437</v>
+        <v>6391704</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123465291</v>
+        <v>123465409</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>57994</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376510</v>
+        <v>376319</v>
       </c>
       <c r="R3" t="n">
-        <v>6391640</v>
+        <v>6391481</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123465014</v>
+        <v>123464851</v>
       </c>
       <c r="B4" t="n">
         <v>57861</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376598</v>
+        <v>375765</v>
       </c>
       <c r="R4" t="n">
-        <v>6391950</v>
+        <v>6391436</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123465129</v>
+        <v>123465181</v>
       </c>
       <c r="B5" t="n">
-        <v>57994</v>
+        <v>96957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102995</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376477</v>
+        <v>375707</v>
       </c>
       <c r="R5" t="n">
-        <v>6391604</v>
+        <v>6391364</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123465181</v>
+        <v>123465014</v>
       </c>
       <c r="B6" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375707</v>
+        <v>376598</v>
       </c>
       <c r="R6" t="n">
-        <v>6391364</v>
+        <v>6391950</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123465409</v>
+        <v>123464678</v>
       </c>
       <c r="B7" t="n">
-        <v>57994</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102995</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376319</v>
+        <v>376617</v>
       </c>
       <c r="R7" t="n">
-        <v>6391481</v>
+        <v>6391973</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123464678</v>
+        <v>123465281</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>56834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,16 +1357,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100065</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376617</v>
+        <v>376361</v>
       </c>
       <c r="R8" t="n">
-        <v>6391973</v>
+        <v>6391616</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123464802</v>
+        <v>123464683</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,20 +1464,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376470</v>
+        <v>376582</v>
       </c>
       <c r="R9" t="n">
-        <v>6391704</v>
+        <v>6391932</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123464683</v>
+        <v>123465291</v>
       </c>
       <c r="B10" t="n">
         <v>57861</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376582</v>
+        <v>376510</v>
       </c>
       <c r="R10" t="n">
-        <v>6391932</v>
+        <v>6391640</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123464851</v>
+        <v>123464849</v>
       </c>
       <c r="B11" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,26 +1690,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375765</v>
+        <v>375785</v>
       </c>
       <c r="R11" t="n">
-        <v>6391436</v>
+        <v>6391437</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123465281</v>
+        <v>123465129</v>
       </c>
       <c r="B12" t="n">
-        <v>56834</v>
+        <v>57994</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,20 +1797,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100065</v>
+        <v>102995</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376361</v>
+        <v>376477</v>
       </c>
       <c r="R12" t="n">
-        <v>6391616</v>
+        <v>6391604</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123464802</v>
+        <v>123464851</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376470</v>
+        <v>375765</v>
       </c>
       <c r="R2" t="n">
-        <v>6391704</v>
+        <v>6391436</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123465409</v>
+        <v>123464802</v>
       </c>
       <c r="B3" t="n">
-        <v>57994</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102995</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376319</v>
+        <v>376470</v>
       </c>
       <c r="R3" t="n">
-        <v>6391481</v>
+        <v>6391704</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123464851</v>
+        <v>123465181</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,26 +913,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375765</v>
+        <v>375707</v>
       </c>
       <c r="R4" t="n">
-        <v>6391436</v>
+        <v>6391364</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123465181</v>
+        <v>123465291</v>
       </c>
       <c r="B5" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,26 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375707</v>
+        <v>376510</v>
       </c>
       <c r="R5" t="n">
-        <v>6391364</v>
+        <v>6391640</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123465014</v>
+        <v>123464849</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376598</v>
+        <v>375785</v>
       </c>
       <c r="R6" t="n">
-        <v>6391950</v>
+        <v>6391437</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123464678</v>
+        <v>123464683</v>
       </c>
       <c r="B7" t="n">
         <v>57861</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376617</v>
+        <v>376582</v>
       </c>
       <c r="R7" t="n">
-        <v>6391973</v>
+        <v>6391932</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123465281</v>
+        <v>123465014</v>
       </c>
       <c r="B8" t="n">
-        <v>56834</v>
+        <v>57861</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,16 +1357,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100065</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376361</v>
+        <v>376598</v>
       </c>
       <c r="R8" t="n">
-        <v>6391616</v>
+        <v>6391950</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123464683</v>
+        <v>123465129</v>
       </c>
       <c r="B9" t="n">
-        <v>57861</v>
+        <v>57994</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,20 +1464,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>102995</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376582</v>
+        <v>376477</v>
       </c>
       <c r="R9" t="n">
-        <v>6391932</v>
+        <v>6391604</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123465291</v>
+        <v>123465409</v>
       </c>
       <c r="B10" t="n">
-        <v>57861</v>
+        <v>57994</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,20 +1575,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>102995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376510</v>
+        <v>376319</v>
       </c>
       <c r="R10" t="n">
-        <v>6391640</v>
+        <v>6391481</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123464849</v>
+        <v>123464678</v>
       </c>
       <c r="B11" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,26 +1690,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375785</v>
+        <v>376617</v>
       </c>
       <c r="R11" t="n">
-        <v>6391437</v>
+        <v>6391973</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123465129</v>
+        <v>123465281</v>
       </c>
       <c r="B12" t="n">
-        <v>57994</v>
+        <v>56834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,20 +1797,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102995</v>
+        <v>100065</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376477</v>
+        <v>376361</v>
       </c>
       <c r="R12" t="n">
-        <v>6391604</v>
+        <v>6391616</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123464802</v>
+        <v>123464849</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>96957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376470</v>
+        <v>375785</v>
       </c>
       <c r="R3" t="n">
-        <v>6391704</v>
+        <v>6391437</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123465181</v>
+        <v>123465281</v>
       </c>
       <c r="B4" t="n">
-        <v>96957</v>
+        <v>56834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375707</v>
+        <v>376361</v>
       </c>
       <c r="R4" t="n">
-        <v>6391364</v>
+        <v>6391616</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123465291</v>
+        <v>123465181</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,26 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376510</v>
+        <v>375707</v>
       </c>
       <c r="R5" t="n">
-        <v>6391640</v>
+        <v>6391364</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123464849</v>
+        <v>123464678</v>
       </c>
       <c r="B6" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1135,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375785</v>
+        <v>376617</v>
       </c>
       <c r="R6" t="n">
-        <v>6391437</v>
+        <v>6391973</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123464683</v>
+        <v>123465129</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>57994</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>102995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376582</v>
+        <v>376477</v>
       </c>
       <c r="R7" t="n">
-        <v>6391932</v>
+        <v>6391604</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123465014</v>
+        <v>123464683</v>
       </c>
       <c r="B8" t="n">
         <v>57861</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376598</v>
+        <v>376582</v>
       </c>
       <c r="R8" t="n">
-        <v>6391950</v>
+        <v>6391932</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123465129</v>
+        <v>123465409</v>
       </c>
       <c r="B9" t="n">
         <v>57994</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376477</v>
+        <v>376319</v>
       </c>
       <c r="R9" t="n">
-        <v>6391604</v>
+        <v>6391481</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123465409</v>
+        <v>123464802</v>
       </c>
       <c r="B10" t="n">
-        <v>57994</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,16 +1579,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102995</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376319</v>
+        <v>376470</v>
       </c>
       <c r="R10" t="n">
-        <v>6391481</v>
+        <v>6391704</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123464678</v>
+        <v>123465014</v>
       </c>
       <c r="B11" t="n">
         <v>57861</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376617</v>
+        <v>376598</v>
       </c>
       <c r="R11" t="n">
-        <v>6391973</v>
+        <v>6391950</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123465281</v>
+        <v>123465291</v>
       </c>
       <c r="B12" t="n">
-        <v>56834</v>
+        <v>57861</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,16 +1801,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100065</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376361</v>
+        <v>376510</v>
       </c>
       <c r="R12" t="n">
-        <v>6391616</v>
+        <v>6391640</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123464851</v>
+        <v>123465181</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375765</v>
+        <v>375707</v>
       </c>
       <c r="R2" t="n">
-        <v>6391436</v>
+        <v>6391364</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123464849</v>
+        <v>123464678</v>
       </c>
       <c r="B3" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375785</v>
+        <v>376617</v>
       </c>
       <c r="R3" t="n">
-        <v>6391437</v>
+        <v>6391973</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123465281</v>
+        <v>123464683</v>
       </c>
       <c r="B4" t="n">
-        <v>56834</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,16 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100065</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376361</v>
+        <v>376582</v>
       </c>
       <c r="R4" t="n">
-        <v>6391616</v>
+        <v>6391932</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123465181</v>
+        <v>123465291</v>
       </c>
       <c r="B5" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,26 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375707</v>
+        <v>376510</v>
       </c>
       <c r="R5" t="n">
-        <v>6391364</v>
+        <v>6391640</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123464678</v>
+        <v>123464802</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,20 +1131,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376617</v>
+        <v>376470</v>
       </c>
       <c r="R6" t="n">
-        <v>6391973</v>
+        <v>6391704</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123465129</v>
+        <v>123464849</v>
       </c>
       <c r="B7" t="n">
-        <v>57994</v>
+        <v>96957</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102995</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376477</v>
+        <v>375785</v>
       </c>
       <c r="R7" t="n">
-        <v>6391604</v>
+        <v>6391437</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123464683</v>
+        <v>123465129</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>57994</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,20 +1353,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>102995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376582</v>
+        <v>376477</v>
       </c>
       <c r="R8" t="n">
-        <v>6391932</v>
+        <v>6391604</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123465409</v>
+        <v>123464851</v>
       </c>
       <c r="B9" t="n">
-        <v>57994</v>
+        <v>57861</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,20 +1464,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102995</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376319</v>
+        <v>375765</v>
       </c>
       <c r="R9" t="n">
-        <v>6391481</v>
+        <v>6391436</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123464802</v>
+        <v>123465014</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,20 +1575,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376470</v>
+        <v>376598</v>
       </c>
       <c r="R10" t="n">
-        <v>6391704</v>
+        <v>6391950</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123465014</v>
+        <v>123465281</v>
       </c>
       <c r="B11" t="n">
-        <v>57861</v>
+        <v>56834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,16 +1690,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100065</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376598</v>
+        <v>376361</v>
       </c>
       <c r="R11" t="n">
-        <v>6391950</v>
+        <v>6391616</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123465291</v>
+        <v>123465409</v>
       </c>
       <c r="B12" t="n">
-        <v>57861</v>
+        <v>57994</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,20 +1797,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>102995</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376510</v>
+        <v>376319</v>
       </c>
       <c r="R12" t="n">
-        <v>6391640</v>
+        <v>6391481</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123465409</v>
+        <v>123465328</v>
       </c>
       <c r="B2" t="n">
-        <v>58016</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102995</v>
+        <v>2606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376319</v>
+        <v>375889</v>
       </c>
       <c r="R2" t="n">
-        <v>6391481</v>
+        <v>6391488</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123464849</v>
+        <v>123464802</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375785</v>
+        <v>376470</v>
       </c>
       <c r="R3" t="n">
-        <v>6391437</v>
+        <v>6391704</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123465181</v>
+        <v>123464813</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375707</v>
+        <v>376527</v>
       </c>
       <c r="R4" t="n">
-        <v>6391364</v>
+        <v>6391601</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123464683</v>
+        <v>123464833</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,16 +1004,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100065</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1043,7 +1023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376582</v>
+        <v>376098</v>
       </c>
       <c r="R5" t="n">
-        <v>6391932</v>
+        <v>6391492</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123465014</v>
+        <v>123465281</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,16 +1110,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100065</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376598</v>
+        <v>376361</v>
       </c>
       <c r="R6" t="n">
-        <v>6391950</v>
+        <v>6391616</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123464678</v>
+        <v>123465248</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,26 +1216,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376617</v>
+        <v>375866</v>
       </c>
       <c r="R7" t="n">
-        <v>6391973</v>
+        <v>6391492</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123465129</v>
+        <v>123464839</v>
       </c>
       <c r="B8" t="n">
-        <v>58016</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102995</v>
+        <v>102987</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376477</v>
+        <v>376072</v>
       </c>
       <c r="R8" t="n">
-        <v>6391604</v>
+        <v>6391486</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1380,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,32 +1417,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123465291</v>
+        <v>123465346</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1487,7 +1447,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376510</v>
+        <v>375868</v>
       </c>
       <c r="R9" t="n">
-        <v>6391640</v>
+        <v>6391491</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,32 +1523,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123464802</v>
+        <v>123464823</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>102995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1607,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376470</v>
+        <v>376300</v>
       </c>
       <c r="R10" t="n">
-        <v>6391704</v>
+        <v>6391462</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,15 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123464851</v>
+        <v>123465129</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,16 +1640,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>102995</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1709,7 +1659,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375765</v>
+        <v>376477</v>
       </c>
       <c r="R11" t="n">
-        <v>6391436</v>
+        <v>6391604</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1698,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123465281</v>
+        <v>123465409</v>
       </c>
       <c r="B12" t="n">
-        <v>56856</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,16 +1746,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100065</v>
+        <v>102995</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1829,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376361</v>
+        <v>376319</v>
       </c>
       <c r="R12" t="n">
-        <v>6391616</v>
+        <v>6391481</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1893,6 +1838,1384 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123464678</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>376617</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6391973</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123464683</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>376582</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6391932</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123464821</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>376400</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6391524</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123464851</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>375765</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6391436</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123465014</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>376598</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6391950</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123465262</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>375889</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6391501</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123465291</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>376510</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6391640</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123465354</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>375888</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6391503</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123464835</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>376076</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6391489</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123464847</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>375967</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6391457</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123464849</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>375785</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6391437</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123465181</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>375707</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6391364</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123465378</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kinnarumma, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>375743</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6391451</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-05-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Inventering på uppdrag av Borås stad</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Svensk Naturförvaltning AB</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27085-2024 artfynd.xlsx
+++ b/artfynd/A 27085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123465328</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123464802</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123464813</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123464833</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123465281</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123465248</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123464839</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123465346</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123464823</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123465129</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123465409</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123464678</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123464683</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123464821</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123464851</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123465014</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123465262</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2580,6 +2670,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123465291</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2686,6 +2781,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123465354</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123464835</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2898,6 +3003,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123464847</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3004,6 +3114,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123464849</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3110,6 +3225,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123465181</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3216,8 +3336,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123465378</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>